--- a/input/timetable/Химия.xlsx
+++ b/input/timetable/Химия.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28755" windowHeight="13980" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28755" windowHeight="13980" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="163">
   <si>
     <t>пара</t>
   </si>
@@ -68,6 +68,9 @@
     <t>Директор института</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -122,6 +125,12 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Бушева Ж.И.</t>
+  </si>
+  <si>
+    <t>Кузнецова А.А.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
@@ -131,15 +140,27 @@
     <t>Неорганическая химия (лек), А310</t>
   </si>
   <si>
+    <t>Крайник В.В.</t>
+  </si>
+  <si>
     <t>Неорганическая химия, п/г1, А121</t>
   </si>
   <si>
     <t>Неорганическая химия, п/г2, А121</t>
   </si>
   <si>
+    <t>Еловой С.Г.</t>
+  </si>
+  <si>
     <t>Правоведение (лек 32 ч)</t>
   </si>
   <si>
+    <t>Владимирова Г.Е.</t>
+  </si>
+  <si>
+    <t>Мурашко Ю.А.</t>
+  </si>
+  <si>
     <t>Химия окружающей среды (пр), А310</t>
   </si>
   <si>
@@ -158,6 +179,9 @@
     <t>Химическая технология (пр), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Торосян В.Ф.</t>
+  </si>
+  <si>
     <t>Анализ природных и техногенных объектов (лек), ЭОиДОТ</t>
   </si>
   <si>
@@ -170,6 +194,12 @@
     <t xml:space="preserve">Зав.кафедрой </t>
   </si>
   <si>
+    <t>Иванов А.В.</t>
+  </si>
+  <si>
+    <t>Коробкин А.В.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, А502</t>
   </si>
   <si>
@@ -203,6 +233,9 @@
     <t>Основы российской государственности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Заводовский А.Г.</t>
+  </si>
+  <si>
     <t>Аналитическая химия (пр), А310</t>
   </si>
   <si>
@@ -221,6 +254,18 @@
     <t xml:space="preserve">Физическая химия (лек), ЭОиДОТ </t>
   </si>
   <si>
+    <t>Сало В.Э.</t>
+  </si>
+  <si>
+    <t>Васильева И.С.</t>
+  </si>
+  <si>
+    <t>Сало В.Э.;Васильева И.С.</t>
+  </si>
+  <si>
+    <t>Сало В.Э.; Васильева И.С.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф.сфере, п/г 1, А502</t>
   </si>
   <si>
@@ -233,12 +278,18 @@
     <t>Коллоидная химия (лек). ЭОиДОТ</t>
   </si>
   <si>
+    <t>Гавриленко М.А.</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
     <t xml:space="preserve">                   РАСПИСАНИЕ УЧЕБНЫХ ЗАНЯТИЙ </t>
   </si>
   <si>
+    <t>Мухутдинов Д.Р.</t>
+  </si>
+  <si>
     <t>2025-2026</t>
   </si>
   <si>
@@ -263,12 +314,39 @@
     <t>02.02.2026-08.04.2026</t>
   </si>
   <si>
+    <t>Гореликов А.В.</t>
+  </si>
+  <si>
+    <t>Ончева Е.М.</t>
+  </si>
+  <si>
+    <t>Мархинин В.В.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А.</t>
+  </si>
+  <si>
+    <t>Сташкин П.Р</t>
+  </si>
+  <si>
+    <t>Теллер Е.В.</t>
+  </si>
+  <si>
+    <t>Еловой С.Г./Ончева Е.М.</t>
+  </si>
+  <si>
     <t>Информатика, п/г 1, А509</t>
   </si>
   <si>
     <t>Информатика, п/г 2, А509</t>
   </si>
   <si>
+    <t>Грамма Д.В.</t>
+  </si>
+  <si>
+    <t>Еловой С.Г;  Подлуцкая К.А.</t>
+  </si>
+  <si>
     <t>Математический анализ (пр), А305</t>
   </si>
   <si>
@@ -302,12 +380,21 @@
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Смирнова И.В.</t>
+  </si>
+  <si>
+    <t>Ашарин А.А.</t>
+  </si>
+  <si>
     <t>Аналитическая химия, п/г 1, А122</t>
   </si>
   <si>
     <t>Аналитическая химия, п/г 2, А122</t>
   </si>
   <si>
+    <t>Чудова Е.С.</t>
+  </si>
+  <si>
     <t>Химия окружающей среды (лек), ЭОиДОТ</t>
   </si>
   <si>
@@ -317,6 +404,12 @@
     <t>Молекулярная физика и термодинамика, п/г 2, А301</t>
   </si>
   <si>
+    <t>Шукурова И.В.; Заводовский А.Г.</t>
+  </si>
+  <si>
+    <t>Заводовский А.Г.;Шукурова И.В.</t>
+  </si>
+  <si>
     <t>Молекулярная физика и термодинамика (лек), А304</t>
   </si>
   <si>
@@ -329,21 +422,42 @@
     <t>Правоведение (пр), А304</t>
   </si>
   <si>
+    <t>Воронина Е.В.</t>
+  </si>
+  <si>
     <t>Основы экономической культуры (лек 32 ч)</t>
   </si>
   <si>
+    <t>Азиева М.Т.</t>
+  </si>
+  <si>
     <t>Органическая химия (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Органическая химия (лаб), А121</t>
   </si>
   <si>
+    <t>Мулюкин М.А.</t>
+  </si>
+  <si>
     <t>Физическая химия (лаб), А124</t>
   </si>
   <si>
+    <t>Севастьянова Е.В.</t>
+  </si>
+  <si>
+    <t>Екимова И.А.</t>
+  </si>
+  <si>
+    <t>Фаррахова Г.Р.</t>
+  </si>
+  <si>
     <t>Физические методы исследования (лаб) А121</t>
   </si>
   <si>
+    <t>Лазарев Д.А.</t>
+  </si>
+  <si>
     <t>Учебная практика, по получению первичных профессиональных умений и навыков, в том числе первичных умений и навыков научно-исследовательской деятельности, А310//</t>
   </si>
   <si>
@@ -356,6 +470,9 @@
     <t>Физические методы исследования (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Бикмухаметова Л.М.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф.сфере, п/г 2, А604</t>
   </si>
   <si>
@@ -377,13 +494,25 @@
     <t>Иностранный язык в профессиональной сфере (24 ч), К429</t>
   </si>
   <si>
+    <t>Джариев И.Э.; Теллер Е.В.</t>
+  </si>
+  <si>
     <t>Механика (лек), А314</t>
   </si>
   <si>
+    <t>Джариев И.Э.</t>
+  </si>
+  <si>
+    <t>Петров Е.А.</t>
+  </si>
+  <si>
     <t>Механика (пр), А320</t>
   </si>
   <si>
     <t xml:space="preserve">Механика, п/г 2, А302 </t>
+  </si>
+  <si>
+    <t>Сарычева Т.А.</t>
   </si>
 </sst>
 </file>
@@ -495,7 +624,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,6 +643,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -525,7 +660,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="69">
     <border>
       <left/>
       <right/>
@@ -646,6 +781,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -685,6 +878,19 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1314,7 +1520,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="294">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1347,28 +1553,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1392,30 +1601,32 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1436,43 +1647,61 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1480,509 +1709,512 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2314,7 +2546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2323,12 +2555,13 @@
     <col min="4" max="4" width="17" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="9.28515625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.28515625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2336,15 +2569,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2352,77 +2585,77 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46">
+      <c r="C6" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="64"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H6" s="83"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="47"/>
-      <c r="E7" s="48" t="s">
-        <v>73</v>
+      <c r="D7" s="50"/>
+      <c r="E7" s="51" t="s">
+        <v>90</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>0</v>
@@ -2433,409 +2666,471 @@
       <c r="D9" s="17"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="21">
+      <c r="G9" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="22">
         <v>3</v>
       </c>
-      <c r="C10" s="98" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="100"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23">
+      <c r="C10" s="128" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="72" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="23"/>
+      <c r="B11" s="24">
         <v>4</v>
       </c>
-      <c r="C11" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="103"/>
-    </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="C11" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24">
         <v>5</v>
       </c>
-      <c r="C12" s="104"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="106"/>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23">
+      <c r="C12" s="131"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="71"/>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="23"/>
+      <c r="B13" s="24">
         <v>6</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="109"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="C13" s="134"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="73"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="28">
         <v>3</v>
       </c>
-      <c r="C14" s="75" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="76"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23">
+      <c r="C14" s="141" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="142"/>
+      <c r="E14" s="143"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="72" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24">
         <v>4</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="81"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23">
+      <c r="C15" s="99" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="74" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24">
         <v>5</v>
       </c>
-      <c r="C16" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
-    </row>
-    <row r="17" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="29"/>
-      <c r="B17" s="30">
+      <c r="C16" s="99" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="74" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="30"/>
+      <c r="B17" s="31">
         <v>6</v>
       </c>
-      <c r="C17" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="81"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30">
+      <c r="C17" s="99" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="101"/>
+      <c r="G17" s="74" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="31">
         <v>7</v>
       </c>
-      <c r="C18" s="91"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="93" t="s">
+      <c r="C18" s="154"/>
+      <c r="D18" s="155"/>
+      <c r="E18" s="156" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="157"/>
+      <c r="G18" s="74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="28">
+        <v>1</v>
+      </c>
+      <c r="C19" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="79" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24">
+        <v>2</v>
+      </c>
+      <c r="C20" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="74" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24">
+        <v>3</v>
+      </c>
+      <c r="C21" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="74" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="29"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="80"/>
+    </row>
+    <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="158"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="103"/>
+      <c r="G23" s="72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23"/>
+      <c r="B24" s="22">
+        <v>3</v>
+      </c>
+      <c r="C24" s="97" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="98"/>
+      <c r="E24" s="104" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="105"/>
+      <c r="G24" s="77" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24">
+        <v>4</v>
+      </c>
+      <c r="C25" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="23"/>
+      <c r="B26" s="24">
+        <v>5</v>
+      </c>
+      <c r="C26" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="30"/>
+      <c r="B27" s="31">
+        <v>6</v>
+      </c>
+      <c r="C27" s="150"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="152" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="153"/>
+      <c r="G27" s="73" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="28">
+        <v>4</v>
+      </c>
+      <c r="C28" s="137" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="102"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="149"/>
+      <c r="G28" s="72" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="33"/>
+      <c r="B29" s="24">
+        <v>5</v>
+      </c>
+      <c r="C29" s="138"/>
+      <c r="D29" s="104"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="73" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="34"/>
+      <c r="B30" s="31">
+        <v>6</v>
+      </c>
+      <c r="C30" s="138"/>
+      <c r="D30" s="104"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="73" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="35"/>
+      <c r="B31" s="26">
+        <v>7</v>
+      </c>
+      <c r="C31" s="139"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="147"/>
+      <c r="G31" s="62" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="28">
+        <v>1</v>
+      </c>
+      <c r="C32" s="118" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="72" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="33"/>
+      <c r="B33" s="37">
+        <v>2</v>
+      </c>
+      <c r="C33" s="124" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="74" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="38"/>
+      <c r="B34" s="26">
+        <v>3</v>
+      </c>
+      <c r="C34" s="115" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="116"/>
+      <c r="E34" s="116"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="62" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="109"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="111"/>
+      <c r="G35" s="41"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="42"/>
+      <c r="B36" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="121" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="123"/>
+      <c r="G36" s="72" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="44"/>
+      <c r="B37" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="94"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="27">
-        <v>1</v>
-      </c>
-      <c r="C19" s="128" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="129"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="130"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23">
-        <v>2</v>
-      </c>
-      <c r="C20" s="101" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="103"/>
-    </row>
-    <row r="21" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23">
-        <v>3</v>
-      </c>
-      <c r="C21" s="101" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="103"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="137"/>
-    </row>
-    <row r="23" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="27">
-        <v>2</v>
-      </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="133"/>
-    </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22"/>
-      <c r="B24" s="21">
-        <v>3</v>
-      </c>
-      <c r="C24" s="131" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" s="132"/>
-      <c r="E24" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="134"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23">
-        <v>4</v>
-      </c>
-      <c r="C25" s="79" t="s">
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="44"/>
+      <c r="B38" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="112" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="113"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="114"/>
+      <c r="G38" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="81"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23">
-        <v>5</v>
-      </c>
-      <c r="C26" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="81"/>
-    </row>
-    <row r="27" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30">
-        <v>6</v>
-      </c>
-      <c r="C27" s="87"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="90"/>
-    </row>
-    <row r="28" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="27">
-        <v>4</v>
-      </c>
-      <c r="C28" s="69" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="70"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="86"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="23">
-        <v>5</v>
-      </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="83"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="32"/>
-      <c r="B30" s="30">
-        <v>6</v>
-      </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="83"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="33"/>
-      <c r="B31" s="25">
-        <v>7</v>
-      </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="84"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="27">
-        <v>1</v>
-      </c>
-      <c r="C32" s="119" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" s="120"/>
-      <c r="E32" s="120"/>
-      <c r="F32" s="121"/>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="31"/>
-      <c r="B33" s="35">
-        <v>2</v>
-      </c>
-      <c r="C33" s="125" t="s">
-        <v>118</v>
-      </c>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
-      <c r="F33" s="127"/>
-    </row>
-    <row r="34" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="25">
-        <v>3</v>
-      </c>
-      <c r="C34" s="116" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="118"/>
-    </row>
-    <row r="35" spans="1:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="110"/>
-      <c r="D35" s="111"/>
-      <c r="E35" s="111"/>
-      <c r="F35" s="112"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="39"/>
-      <c r="B36" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="123"/>
-      <c r="E36" s="123"/>
-      <c r="F36" s="124"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="113" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="114"/>
-      <c r="E37" s="114"/>
-      <c r="F37" s="115"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="41"/>
-      <c r="B38" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="113" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="114"/>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
-    </row>
-    <row r="39" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="43"/>
-      <c r="B39" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="116" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="117"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="118"/>
-    </row>
-    <row r="40" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="46"/>
+      <c r="B39" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="62" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C28:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C14:D14"/>
@@ -2852,6 +3147,29 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2882,7 +3200,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2891,10 +3209,11 @@
     <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="19" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2902,15 +3221,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2918,449 +3237,533 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="58"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M5" s="63"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46">
+      <c r="C6" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49">
         <v>2</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="48" t="s">
-        <v>56</v>
+      <c r="D7" s="58"/>
+      <c r="E7" s="51" t="s">
+        <v>66</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+    </row>
+    <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="52"/>
-    </row>
-    <row r="10" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="160"/>
-      <c r="E10" s="160"/>
-      <c r="F10" s="161"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23">
+      <c r="D9" s="53"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="206"/>
+      <c r="E10" s="206"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="67"/>
+    </row>
+    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="23"/>
+      <c r="B11" s="24">
         <v>3</v>
       </c>
-      <c r="C11" s="156" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="158"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="C11" s="202" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="203"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="69"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24">
         <v>7</v>
       </c>
-      <c r="C12" s="138" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
-    </row>
-    <row r="13" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="187" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="188"/>
+      <c r="E12" s="188"/>
+      <c r="F12" s="189"/>
+      <c r="G12" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>8</v>
       </c>
-      <c r="C13" s="150" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="152"/>
-    </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="C13" s="199" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="62" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="28">
         <v>1</v>
       </c>
-      <c r="C14" s="162" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="163"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="164"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23">
+      <c r="C14" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+      <c r="F14" s="210"/>
+      <c r="G14" s="72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24">
         <v>3</v>
       </c>
-      <c r="C15" s="153" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
-      <c r="F15" s="155"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23">
+      <c r="C15" s="164" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="165"/>
+      <c r="E15" s="165"/>
+      <c r="F15" s="161"/>
+      <c r="G15" s="73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24">
         <v>4</v>
       </c>
-      <c r="C16" s="165" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="166"/>
-      <c r="E16" s="166"/>
-      <c r="F16" s="167"/>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23">
+      <c r="C16" s="211" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+      <c r="F16" s="213"/>
+      <c r="G16" s="73" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24">
         <v>5</v>
       </c>
-      <c r="C17" s="153" t="s">
+      <c r="C17" s="164" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="154"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="155"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30">
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="31">
         <v>6</v>
       </c>
-      <c r="C18" s="141"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="143"/>
-    </row>
-    <row r="19" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="27">
+      <c r="C18" s="190"/>
+      <c r="D18" s="191"/>
+      <c r="E18" s="191"/>
+      <c r="F18" s="192"/>
+      <c r="G18" s="32"/>
+    </row>
+    <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="28">
         <v>2</v>
       </c>
-      <c r="C19" s="168" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="169"/>
-      <c r="E19" s="169"/>
-      <c r="F19" s="170"/>
-    </row>
-    <row r="20" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23">
+      <c r="C19" s="214" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="215"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="72" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24">
         <v>3</v>
       </c>
-      <c r="C20" s="153" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="175"/>
-      <c r="E20" s="193" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="155"/>
-    </row>
-    <row r="21" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23">
+      <c r="C20" s="164" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="219"/>
+      <c r="E20" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="161"/>
+      <c r="G20" s="73" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24">
         <v>4</v>
       </c>
-      <c r="C21" s="171" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="172"/>
-      <c r="E21" s="173" t="s">
-        <v>96</v>
-      </c>
-      <c r="F21" s="174"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="25">
+      <c r="C21" s="217" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="218"/>
+      <c r="E21" s="170" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" s="171"/>
+      <c r="G21" s="73" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="29"/>
+      <c r="B22" s="26">
         <v>5</v>
       </c>
-      <c r="C22" s="144" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="145"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="146"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="C22" s="193" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="195"/>
+      <c r="G22" s="62" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="22">
         <v>1</v>
       </c>
-      <c r="C23" s="147" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="149"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22"/>
-      <c r="B24" s="21">
+      <c r="C23" s="196" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="197"/>
+      <c r="E23" s="197"/>
+      <c r="F23" s="198"/>
+      <c r="G23" s="77" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23"/>
+      <c r="B24" s="22">
         <v>2</v>
       </c>
-      <c r="C24" s="153" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" s="154"/>
-      <c r="E24" s="154"/>
-      <c r="F24" s="155"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="28"/>
-      <c r="B25" s="25">
+      <c r="C24" s="164" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="165"/>
+      <c r="E24" s="165"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="29"/>
+      <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="195" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="196"/>
-      <c r="E25" s="196"/>
-      <c r="F25" s="197"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="27">
+      <c r="C25" s="166" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="167"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="82"/>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="28">
         <v>1</v>
       </c>
-      <c r="C26" s="181"/>
-      <c r="D26" s="182"/>
-      <c r="E26" s="182"/>
-      <c r="F26" s="183"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="31"/>
-      <c r="B27" s="23">
+      <c r="C26" s="176"/>
+      <c r="D26" s="177"/>
+      <c r="E26" s="177"/>
+      <c r="F26" s="178"/>
+      <c r="G26" s="67"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="33"/>
+      <c r="B27" s="24">
         <v>2</v>
       </c>
-      <c r="C27" s="176" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="173"/>
-      <c r="E27" s="173"/>
-      <c r="F27" s="174"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="23">
+      <c r="C27" s="169" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="170"/>
+      <c r="E27" s="170"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="73" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="33"/>
+      <c r="B28" s="24">
         <v>3</v>
       </c>
-      <c r="C28" s="194"/>
-      <c r="D28" s="189"/>
-      <c r="E28" s="126" t="s">
-        <v>93</v>
-      </c>
-      <c r="F28" s="127"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="23">
+      <c r="C28" s="162"/>
+      <c r="D28" s="163"/>
+      <c r="E28" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="126"/>
+      <c r="G28" s="73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="33"/>
+      <c r="B29" s="24">
         <v>4</v>
       </c>
-      <c r="C29" s="194"/>
-      <c r="D29" s="189"/>
-      <c r="E29" s="126" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="127"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="33"/>
-      <c r="B30" s="25">
+      <c r="C29" s="162"/>
+      <c r="D29" s="163"/>
+      <c r="E29" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="126"/>
+      <c r="G29" s="73" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="26">
         <v>5</v>
       </c>
-      <c r="C30" s="91"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="93" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="94"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="27">
+      <c r="C30" s="154"/>
+      <c r="D30" s="155"/>
+      <c r="E30" s="156" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="157"/>
+      <c r="G30" s="62" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="28">
         <v>1</v>
       </c>
-      <c r="C31" s="191" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="192"/>
-      <c r="E31" s="187"/>
-      <c r="F31" s="188"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="41"/>
-      <c r="B32" s="23">
+      <c r="C31" s="185" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="186"/>
+      <c r="E31" s="182"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="72" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="44"/>
+      <c r="B32" s="24">
         <v>2</v>
       </c>
-      <c r="C32" s="125" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" s="126"/>
-      <c r="E32" s="189"/>
-      <c r="F32" s="190"/>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="54"/>
-      <c r="B33" s="30">
+      <c r="C32" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="125"/>
+      <c r="E32" s="163"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="57"/>
+      <c r="B33" s="31">
         <v>3</v>
       </c>
-      <c r="C33" s="125" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="126"/>
-      <c r="E33" s="189"/>
-      <c r="F33" s="190"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="25">
+      <c r="C33" s="124" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="125"/>
+      <c r="E33" s="163"/>
+      <c r="F33" s="184"/>
+      <c r="G33" s="74" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="38"/>
+      <c r="B34" s="26">
         <v>4</v>
       </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="180"/>
-    </row>
-    <row r="35" spans="1:6" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="177"/>
-      <c r="D35" s="178"/>
-      <c r="E35" s="178"/>
-      <c r="F35" s="179"/>
-    </row>
-    <row r="36" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="65"/>
-      <c r="B36" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="184" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" s="185"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="186"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="36"/>
-      <c r="B37" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="116" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="118"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="154"/>
+      <c r="D34" s="155"/>
+      <c r="E34" s="155"/>
+      <c r="F34" s="175"/>
+      <c r="G34" s="62"/>
+    </row>
+    <row r="35" spans="1:7" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="172"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="41"/>
+    </row>
+    <row r="36" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="84"/>
+      <c r="B36" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="179" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="180"/>
+      <c r="E36" s="180"/>
+      <c r="F36" s="181"/>
+      <c r="G36" s="86" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="38"/>
+      <c r="B37" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="115" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C35:F35"/>
@@ -3377,22 +3780,11 @@
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3423,7 +3815,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3431,10 +3823,11 @@
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="5" width="17.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3442,15 +3835,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3458,76 +3851,76 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46">
+      <c r="C6" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49">
         <v>3</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="48" t="s">
-        <v>46</v>
+      <c r="D7" s="58"/>
+      <c r="E7" s="51" t="s">
+        <v>54</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>0</v>
@@ -3538,372 +3931,429 @@
       <c r="D9" s="17"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="21">
+      <c r="G9" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="22">
         <v>2</v>
       </c>
-      <c r="C10" s="204"/>
-      <c r="D10" s="205"/>
-      <c r="E10" s="205"/>
-      <c r="F10" s="206"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23">
+      <c r="C10" s="242"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="59"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="23"/>
+      <c r="B11" s="24">
         <v>3</v>
       </c>
-      <c r="C11" s="207" t="s">
+      <c r="C11" s="226" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="227"/>
+      <c r="E11" s="227"/>
+      <c r="F11" s="228"/>
+      <c r="G11" s="73" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24">
+        <v>4</v>
+      </c>
+      <c r="C12" s="226" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="227"/>
+      <c r="E12" s="227"/>
+      <c r="F12" s="228"/>
+      <c r="G12" s="73" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="23"/>
+      <c r="B13" s="24">
+        <v>5</v>
+      </c>
+      <c r="C13" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
-      <c r="F11" s="209"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="D13" s="188"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="189"/>
+      <c r="G13" s="71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
+        <v>6</v>
+      </c>
+      <c r="C14" s="199" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="201"/>
+      <c r="G14" s="80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="121" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="59"/>
+    </row>
+    <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24">
         <v>4</v>
       </c>
-      <c r="C12" s="207" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="208"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="209"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23">
+      <c r="C16" s="187"/>
+      <c r="D16" s="188"/>
+      <c r="E16" s="188"/>
+      <c r="F16" s="189"/>
+      <c r="G16" s="71"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24">
         <v>5</v>
       </c>
-      <c r="C13" s="138" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="140"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="C17" s="187" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="188"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="71" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="29"/>
+      <c r="B18" s="26">
         <v>6</v>
       </c>
-      <c r="C14" s="150" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="151"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="152"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="122" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="123"/>
-      <c r="E15" s="123"/>
-      <c r="F15" s="124"/>
-    </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23">
+      <c r="C18" s="233" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="235"/>
+      <c r="G18" s="62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="28">
+        <v>5</v>
+      </c>
+      <c r="C19" s="248"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="250"/>
+      <c r="G19" s="70"/>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24">
+        <v>6</v>
+      </c>
+      <c r="C20" s="211" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="212"/>
+      <c r="E20" s="212"/>
+      <c r="F20" s="213"/>
+      <c r="G20" s="73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24">
+        <v>7</v>
+      </c>
+      <c r="C21" s="220" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="221"/>
+      <c r="E21" s="221"/>
+      <c r="F21" s="222"/>
+      <c r="G21" s="73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="29"/>
+      <c r="B22" s="26">
+        <v>8</v>
+      </c>
+      <c r="C22" s="223" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="224"/>
+      <c r="E22" s="224"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="230" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="231"/>
+      <c r="E23" s="231"/>
+      <c r="F23" s="232"/>
+      <c r="G23" s="72" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23"/>
+      <c r="B24" s="24">
+        <v>6</v>
+      </c>
+      <c r="C24" s="226" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="227"/>
+      <c r="E24" s="227"/>
+      <c r="F24" s="228"/>
+      <c r="G24" s="73" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24">
+        <v>7</v>
+      </c>
+      <c r="C25" s="226" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="227"/>
+      <c r="E25" s="227"/>
+      <c r="F25" s="228"/>
+      <c r="G25" s="73" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="29"/>
+      <c r="B26" s="26">
+        <v>8</v>
+      </c>
+      <c r="C26" s="226" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="227"/>
+      <c r="E26" s="227"/>
+      <c r="F26" s="228"/>
+      <c r="G26" s="73" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="28">
+        <v>1</v>
+      </c>
+      <c r="C27" s="245"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="247"/>
+      <c r="G27" s="67"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="33"/>
+      <c r="B28" s="24">
+        <v>2</v>
+      </c>
+      <c r="C28" s="187" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="188"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="189"/>
+      <c r="G28" s="71" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="33"/>
+      <c r="B29" s="24">
+        <v>3</v>
+      </c>
+      <c r="C29" s="187" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="188"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="189"/>
+      <c r="G29" s="71" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="26">
         <v>4</v>
       </c>
-      <c r="C16" s="138"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="140"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23">
-        <v>5</v>
-      </c>
-      <c r="C17" s="138" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="139"/>
-      <c r="E17" s="139"/>
-      <c r="F17" s="140"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="28"/>
-      <c r="B18" s="25">
-        <v>6</v>
-      </c>
-      <c r="C18" s="198" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="199"/>
-      <c r="E18" s="199"/>
-      <c r="F18" s="200"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="27">
-        <v>5</v>
-      </c>
-      <c r="C19" s="213"/>
-      <c r="D19" s="214"/>
-      <c r="E19" s="214"/>
-      <c r="F19" s="215"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23">
-        <v>6</v>
-      </c>
-      <c r="C20" s="165" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="166"/>
-      <c r="E20" s="166"/>
-      <c r="F20" s="167"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23">
-        <v>7</v>
-      </c>
-      <c r="C21" s="223" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="224"/>
-      <c r="E21" s="224"/>
-      <c r="F21" s="225"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="25">
-        <v>8</v>
-      </c>
-      <c r="C22" s="226" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="227"/>
-      <c r="E22" s="227"/>
-      <c r="F22" s="228"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="27">
+      <c r="C30" s="233"/>
+      <c r="D30" s="234"/>
+      <c r="E30" s="234"/>
+      <c r="F30" s="235"/>
+      <c r="G30" s="62"/>
+    </row>
+    <row r="31" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="28">
+        <v>1</v>
+      </c>
+      <c r="C31" s="230" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="231"/>
+      <c r="E31" s="231"/>
+      <c r="F31" s="232"/>
+      <c r="G31" s="72" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="44"/>
+      <c r="B32" s="22">
         <v>2</v>
       </c>
-      <c r="C23" s="216" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="217"/>
-      <c r="E23" s="217"/>
-      <c r="F23" s="218"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="22"/>
-      <c r="B24" s="23">
-        <v>6</v>
-      </c>
-      <c r="C24" s="207" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" s="208"/>
-      <c r="E24" s="208"/>
-      <c r="F24" s="209"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23">
-        <v>7</v>
-      </c>
-      <c r="C25" s="207" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="208"/>
-      <c r="E25" s="208"/>
-      <c r="F25" s="209"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="28"/>
-      <c r="B26" s="25">
-        <v>8</v>
-      </c>
-      <c r="C26" s="207" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="208"/>
-      <c r="E26" s="208"/>
-      <c r="F26" s="209"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="27">
-        <v>1</v>
-      </c>
-      <c r="C27" s="210"/>
-      <c r="D27" s="211"/>
-      <c r="E27" s="211"/>
-      <c r="F27" s="212"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="23">
-        <v>2</v>
-      </c>
-      <c r="C28" s="138" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="139"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="140"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="23">
+      <c r="C32" s="211" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="212"/>
+      <c r="E32" s="212"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="44"/>
+      <c r="B33" s="24">
         <v>3</v>
       </c>
-      <c r="C29" s="138" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="140"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="33"/>
-      <c r="B30" s="25">
+      <c r="C33" s="202" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="203"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="73" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="57"/>
+      <c r="B34" s="31">
         <v>4</v>
       </c>
-      <c r="C30" s="198"/>
-      <c r="D30" s="199"/>
-      <c r="E30" s="199"/>
-      <c r="F30" s="200"/>
-    </row>
-    <row r="31" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="27">
-        <v>1</v>
-      </c>
-      <c r="C31" s="216" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" s="217"/>
-      <c r="E31" s="217"/>
-      <c r="F31" s="218"/>
-    </row>
-    <row r="32" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="41"/>
-      <c r="B32" s="21">
-        <v>2</v>
-      </c>
-      <c r="C32" s="165" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="166"/>
-      <c r="E32" s="166"/>
-      <c r="F32" s="167"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="41"/>
-      <c r="B33" s="23">
-        <v>3</v>
-      </c>
-      <c r="C33" s="156" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="157"/>
-      <c r="E33" s="157"/>
-      <c r="F33" s="158"/>
-    </row>
-    <row r="34" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="54"/>
-      <c r="B34" s="30">
-        <v>4</v>
-      </c>
-      <c r="C34" s="156" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="157"/>
-      <c r="E34" s="157"/>
-      <c r="F34" s="158"/>
-    </row>
-    <row r="35" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="67"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="220"/>
-      <c r="D35" s="221"/>
-      <c r="E35" s="221"/>
-      <c r="F35" s="222"/>
-    </row>
-    <row r="36" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="59"/>
-      <c r="B36" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="201" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" s="202"/>
-      <c r="E36" s="202"/>
-      <c r="F36" s="203"/>
-    </row>
-    <row r="37" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="62" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="63"/>
-      <c r="C37" s="219" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="219"/>
-      <c r="E37" s="219"/>
-      <c r="F37" s="219"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="202" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="204"/>
+      <c r="G34" s="73" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="87"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="236"/>
+      <c r="D35" s="237"/>
+      <c r="E35" s="237"/>
+      <c r="F35" s="238"/>
+      <c r="G35" s="89"/>
+    </row>
+    <row r="36" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="64"/>
+      <c r="B36" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="239" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="240"/>
+      <c r="E36" s="240"/>
+      <c r="F36" s="241"/>
+      <c r="G36" s="90" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="76"/>
+      <c r="C37" s="229" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
@@ -3920,6 +4370,19 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C26:F26"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3950,7 +4413,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3959,10 +4422,11 @@
     <col min="4" max="4" width="20.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3970,15 +4434,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3986,86 +4450,86 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="46">
+      <c r="C6" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="49">
         <v>4</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="48" t="s">
-        <v>28</v>
+      <c r="D7" s="58"/>
+      <c r="E7" s="51" t="s">
+        <v>29</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="61"/>
+      <c r="E8" s="51"/>
+    </row>
+    <row r="9" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="97" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="97"/>
-      <c r="E9" s="48"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="127"/>
+      <c r="E9" s="51"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>0</v>
@@ -4076,377 +4540,465 @@
       <c r="D10" s="17"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="21">
+      <c r="G10" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="22">
         <v>1</v>
       </c>
-      <c r="C11" s="223" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="224"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="225"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="C11" s="220" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="221"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24">
         <v>2</v>
       </c>
-      <c r="C12" s="156" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="157"/>
-      <c r="E12" s="157"/>
-      <c r="F12" s="158"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23">
+      <c r="C12" s="202" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="203"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="23"/>
+      <c r="B13" s="24">
         <v>3</v>
       </c>
-      <c r="C13" s="156" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="157"/>
-      <c r="E13" s="157"/>
-      <c r="F13" s="158"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="C13" s="202" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <v>4</v>
       </c>
-      <c r="C14" s="235" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="236"/>
-      <c r="E14" s="236"/>
-      <c r="F14" s="237"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="27">
+      <c r="C14" s="266" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="28">
         <v>1</v>
       </c>
-      <c r="C15" s="168" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="169"/>
-      <c r="E15" s="182"/>
-      <c r="F15" s="183"/>
-    </row>
-    <row r="16" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23">
+      <c r="C15" s="214" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="215"/>
+      <c r="E15" s="177"/>
+      <c r="F15" s="178"/>
+      <c r="G15" s="72" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24">
         <v>2</v>
       </c>
-      <c r="C16" s="257" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="258"/>
-      <c r="E16" s="255"/>
-      <c r="F16" s="256"/>
-    </row>
-    <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23">
+      <c r="C16" s="269" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="270"/>
+      <c r="E16" s="262"/>
+      <c r="F16" s="263"/>
+      <c r="G16" s="73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24">
         <v>3</v>
       </c>
-      <c r="C17" s="125" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="126"/>
-      <c r="E17" s="250"/>
-      <c r="F17" s="251"/>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23">
+      <c r="C17" s="124" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="125"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="265"/>
+      <c r="G17" s="73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24">
         <v>4</v>
       </c>
-      <c r="C18" s="125" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="127"/>
-    </row>
-    <row r="19" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="25">
+      <c r="C18" s="124" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="73" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="29"/>
+      <c r="B19" s="26">
         <v>5</v>
       </c>
-      <c r="C19" s="254" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="90"/>
-    </row>
-    <row r="20" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="27">
+      <c r="C19" s="261" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="28">
         <v>1</v>
       </c>
-      <c r="C20" s="259" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="260"/>
-      <c r="E20" s="260"/>
-      <c r="F20" s="261"/>
-    </row>
-    <row r="21" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23">
+      <c r="C20" s="271" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="272"/>
+      <c r="E20" s="272"/>
+      <c r="F20" s="273"/>
+      <c r="G20" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24">
         <v>2</v>
       </c>
-      <c r="C21" s="235" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="236"/>
-      <c r="E21" s="236"/>
-      <c r="F21" s="237"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23">
+      <c r="C21" s="266" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="267"/>
+      <c r="E21" s="267"/>
+      <c r="F21" s="268"/>
+      <c r="G21" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" s="23"/>
+      <c r="B22" s="24">
         <v>4</v>
       </c>
-      <c r="C22" s="264"/>
-      <c r="D22" s="266"/>
-      <c r="E22" s="269" t="s">
+      <c r="C22" s="253"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="258" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="204"/>
+      <c r="G22" s="71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" s="23"/>
+      <c r="B23" s="24">
+        <v>5</v>
+      </c>
+      <c r="C23" s="253"/>
+      <c r="D23" s="255"/>
+      <c r="E23" s="125" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="126"/>
+      <c r="G23" s="71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="29"/>
+      <c r="B24" s="26">
+        <v>6</v>
+      </c>
+      <c r="C24" s="256"/>
+      <c r="D24" s="257"/>
+      <c r="E24" s="259" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="260"/>
+      <c r="G24" s="80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="28">
+        <v>2</v>
+      </c>
+      <c r="C25" s="251"/>
+      <c r="D25" s="252"/>
+      <c r="E25" s="197" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="198"/>
+      <c r="G25" s="78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="23"/>
+      <c r="B26" s="24">
+        <v>3</v>
+      </c>
+      <c r="C26" s="253"/>
+      <c r="D26" s="254"/>
+      <c r="E26" s="125" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="126"/>
+      <c r="G26" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="J26" s="66"/>
+    </row>
+    <row r="27" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="23"/>
+      <c r="B27" s="24">
+        <v>4</v>
+      </c>
+      <c r="C27" s="202" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="203"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="29"/>
+      <c r="B28" s="26">
+        <v>5</v>
+      </c>
+      <c r="C28" s="266" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="267"/>
+      <c r="E28" s="267"/>
+      <c r="F28" s="268"/>
+      <c r="G28" s="71" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="28">
+        <v>1</v>
+      </c>
+      <c r="C29" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="123"/>
+      <c r="G29" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="158"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="22"/>
-      <c r="B23" s="23">
-        <v>5</v>
-      </c>
-      <c r="C23" s="264"/>
-      <c r="D23" s="266"/>
-      <c r="E23" s="126" t="s">
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="33"/>
+      <c r="B30" s="24">
+        <v>2</v>
+      </c>
+      <c r="C30" s="124" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="127"/>
-    </row>
-    <row r="24" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="28"/>
-      <c r="B24" s="25">
+    </row>
+    <row r="31" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="33"/>
+      <c r="B31" s="24">
         <v>6</v>
       </c>
-      <c r="C24" s="267"/>
-      <c r="D24" s="268"/>
-      <c r="E24" s="270" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="271"/>
-    </row>
-    <row r="25" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="27">
+      <c r="C31" s="280" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="281"/>
+      <c r="E31" s="264"/>
+      <c r="F31" s="265"/>
+      <c r="G31" s="73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" s="34"/>
+      <c r="B32" s="31">
+        <v>7</v>
+      </c>
+      <c r="C32" s="282"/>
+      <c r="D32" s="283"/>
+      <c r="E32" s="163"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="35"/>
+      <c r="B33" s="26">
+        <v>8</v>
+      </c>
+      <c r="C33" s="284"/>
+      <c r="D33" s="285"/>
+      <c r="E33" s="163"/>
+      <c r="F33" s="184"/>
+      <c r="G33" s="62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="22">
+        <v>1</v>
+      </c>
+      <c r="C34" s="205"/>
+      <c r="D34" s="293"/>
+      <c r="E34" s="286" t="s">
+        <v>65</v>
+      </c>
+      <c r="F34" s="287"/>
+      <c r="G34" s="77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="44"/>
+      <c r="B35" s="24">
         <v>2</v>
       </c>
-      <c r="C25" s="262"/>
-      <c r="D25" s="263"/>
-      <c r="E25" s="148" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="149"/>
-    </row>
-    <row r="26" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23">
+      <c r="C35" s="202" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="292"/>
+      <c r="E35" s="288"/>
+      <c r="F35" s="289"/>
+      <c r="G35" s="81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="44"/>
+      <c r="B36" s="24">
         <v>3</v>
       </c>
-      <c r="C26" s="264"/>
-      <c r="D26" s="265"/>
-      <c r="E26" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="F26" s="127"/>
-      <c r="I26" s="61"/>
-    </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="22"/>
-      <c r="B27" s="23">
+      <c r="C36" s="202" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="292"/>
+      <c r="E36" s="290"/>
+      <c r="F36" s="291"/>
+      <c r="G36" s="73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="44"/>
+      <c r="B37" s="24">
         <v>4</v>
       </c>
-      <c r="C27" s="156" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="157"/>
-      <c r="E27" s="157"/>
-      <c r="F27" s="158"/>
-    </row>
-    <row r="28" spans="1:9" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="28"/>
-      <c r="B28" s="25">
-        <v>5</v>
-      </c>
-      <c r="C28" s="235" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="236"/>
-      <c r="E28" s="236"/>
-      <c r="F28" s="237"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="27">
-        <v>1</v>
-      </c>
-      <c r="C29" s="122" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="123"/>
-      <c r="E29" s="123"/>
-      <c r="F29" s="124"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="31"/>
-      <c r="B30" s="23">
-        <v>2</v>
-      </c>
-      <c r="C30" s="125" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="127"/>
-    </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="23">
-        <v>6</v>
-      </c>
-      <c r="C31" s="238" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="239"/>
-      <c r="E31" s="250"/>
-      <c r="F31" s="251"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="32"/>
-      <c r="B32" s="30">
-        <v>7</v>
-      </c>
-      <c r="C32" s="240"/>
-      <c r="D32" s="241"/>
-      <c r="E32" s="189"/>
-      <c r="F32" s="190"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="33"/>
-      <c r="B33" s="25">
-        <v>8</v>
-      </c>
-      <c r="C33" s="242"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="189"/>
-      <c r="F33" s="190"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="21">
-        <v>1</v>
-      </c>
-      <c r="C34" s="159"/>
-      <c r="D34" s="253"/>
-      <c r="E34" s="244" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="245"/>
-    </row>
-    <row r="35" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="41"/>
-      <c r="B35" s="23">
-        <v>2</v>
-      </c>
-      <c r="C35" s="156" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="252"/>
-      <c r="E35" s="246"/>
-      <c r="F35" s="247"/>
-    </row>
-    <row r="36" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="41"/>
-      <c r="B36" s="23">
-        <v>3</v>
-      </c>
-      <c r="C36" s="156" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="252"/>
-      <c r="E36" s="248"/>
-      <c r="F36" s="249"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="41"/>
-      <c r="B37" s="23">
-        <v>4</v>
-      </c>
-      <c r="C37" s="229" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="230"/>
-      <c r="E37" s="230"/>
-      <c r="F37" s="231"/>
-    </row>
-    <row r="38" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="43"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="232"/>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="234"/>
-    </row>
-    <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C37" s="274" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="275"/>
+      <c r="E37" s="275"/>
+      <c r="F37" s="276"/>
+      <c r="G37" s="73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="46"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="277"/>
+      <c r="D38" s="278"/>
+      <c r="E38" s="278"/>
+      <c r="F38" s="279"/>
+      <c r="G38" s="68"/>
+    </row>
+    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:D33"/>
+    <mergeCell ref="E34:F36"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C18:F18"/>
@@ -4463,19 +5015,16 @@
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:D33"/>
-    <mergeCell ref="E34:F36"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
